--- a/data_extactor/batch_10_fa/batch_0098_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0098_fa.xlsx
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>مانیتورینگ | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>امنیت و ایمنی عمومی | زبان انگلیسی</t>
+          <t>ایمنی و امنیت عمومی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ترتیب‌دهی به اطلاعات | بینایی نزدیک | توجه شنیداری | بینایی دور | دقت کنترل | توجه انتخابی | وضوح گفتار | تشخیص گفتار | حساسیت شنوایی | زمان عکس‌العمل | ثبات دست و بازو | سرعت ادراکی | حساسیت به مسئله | بیان شفاهی | درک شفاهی</t>
+          <t>ترتیب‌دهی اطلاعات | بینایی نزدیک | توجه شنیداری | بینایی دور | دقت کنترل | توجه انتخابی | وضوح گفتار | تشخیص گفتار | حساسیت شنوایی | زمان عکس‌العمل | ثبات دست و بازو | سرعت ادراکی | حساسیت به مسئله | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>داخل ساختمان، کنترل‌شده از نظر دما و رطوبت | مکالمات تلفنی | ارتباط با دیگران | پیامد اشتباه | آزادی در تصمیم‌گیری | اهمیت دقیق بودن یا صحت بالا | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | اهمیت تکرار وظایف یکسان</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | ارتباط با دیگران | پیامد خطا | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کاپیتان‌ها، افسران و خلبانان شناورهای آبی | اپراتورهای جرثقیل و برج | اپراتورهای لایروب | نصاب‌ها و تعمیرکاران خطوط انتقال نیروی برق | کارگران نگهداری بزرگراه | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و لیفتراک صنعتی | قفل‌سازان و تعمیرکاران گاوصندوق | مهندسان لوکوموتیو | اپراتورهای قایق موتوری | مهندسان راهبر و سایر اپراتورهای تجهیزات ساخت‌وساز | مهندسان محوطه راه‌آهن، اپراتورهای دینکی و هاستلرها | ترمزبانان، متصدیان سیگنال و سوزنبانان راه‌آهن و آتش‌کاران لوکوموتیو | لوکوموتیورانان و روسای ایستگاه راه‌آهن | ریگرها | ملوانان و روغن‌کاران دریایی | نگهبانان امنیتی | مهندسان کشتی | تعمیرکاران سیگنال و سوزن ریل | بارگیران واگن‌های مخزنی، کامیون‌ها و کشتی‌ها</t>
+          <t>ناخدایان، افسران دوم و راهنمایان شناورهای دریایی | اپراتورهای جرثقیل و تاور | اپراتورهای لایروب | نصابان و تعمیرکاران خطوط انتقال نیروی برق | کارگران نگهداری بزرگراه‌ها | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون صنعتی | قفل‌سازان و تعمیرکاران گاوصندوق | مهندسان لوکوموتیو | اپراتورهای قایق موتوری | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | مهندسان محوطه راه‌آهن، اپراتورهای لکوموتیو مانوری و متصدیان آماده‌سازی لکوموتیو | اپراتورهای ترمز، علائم و سوزن راه‌آهن و آتش‌کاران لکوموتیو | رئیس قطارها و مدیران محوطه راه‌آهن | ریگرها | ملوانان و روغن‌کاران دریایی | نگهبانان امنیتی | مهندسان کشتی | تعمیرکاران سیگنال و سوزن ریل | بارگیران واگن مخزنی، کامیون و کشتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -570,22 +570,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | ترابری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | حمل و نقل</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بینایی دور | درک شفاهی | بیان شفاهی | تشخیص گفتار | بینایی نزدیک | وضوح گفتار | حساسیت به مسئله | جهت‌یابی فضایی | استدلال استقرایی | استدلال قیاسی | دقت کنترل | توجه انتخابی | ترتیب‌دهی به اطلاعات | درک عمق | هماهنگی چندعضوی</t>
+          <t>بینایی دور | درک شفاهی | بیان شفاهی | تشخیص گفتار | بینایی نزدیک | وضوح گفتار | حساسیت به مسئله | جهت‌گیری فضایی | استدلال استقرایی | استدلال قیاسی | دقت کنترل | توجه انتخابی | ترتیب‌دهی اطلاعات | درک عمق | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | درون یک وسیله نقلیه محصور یا کار با تجهیزات محصور | اهمیت دقیق بودن یا صحت بالا | نزدیکی فیزیکی | صرف زمان برای پیاده‌روی یا دویدن | کار با یک گروه کاری یا تیم یا مشارکت در آن | صرف زمان برای انجام حرکات تکراری | مکالمات تلفنی | فضای باز، در معرض تمام شرایط آب و هوایی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | در معرض آلاینده‌ها</t>
+          <t>ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | اهمیت دقیق یا درست بودن | نزدیکی فیزیکی | صرف زمان برای راه رفتن یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | مکالمات تلفنی | فضای باز، در معرض تمام شرایط آب و هوایی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | قرار گرفتن در معرض آلاینده‌ها</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>متصدیان تفریحات و سرگرمی | باربران چمدان و پادوهای هتل | رانندگان اتوبوس، ترانزیت و بین‌شهری | صندوق‌داران | دربانان هتل (کانسیرج) | متصدیان باجه و اجاره | دیسپچرها، به جز پلیس، آتش‌نشانی و آمبولانس | رانندگان/کارگران فروش | سروکنندگان غذا، غیررستورانی | رانندگان کامیون‌های سنگین و تریلی | متصدیان پذیرش هتل، متل و اقامتگاه | اپراتورهای تراکتور و لیفتراک صنعتی | رانندگان کامیونت | متصدیان رختکن و اتاق پرو | ماموران اجرای مقررات پارکینگ | متصدیان مسافران | لوکوموتیورانان و روسای ایستگاه راه‌آهن | ماموران فروش بلیط رزرو و حمل‌ونقل و کارمندان سفر | رانندگان شاتل و شوفرها | رانندگان تاکسی</t>
+          <t>متصدیان تفریح و سرگرمی | باربران چمدان و پادوهای هتل | رانندگان اتوبوس، ترانزیت و بین‌شهری | صندوق‌داران | کانسرج‌ها | کارمندان باجه و اجاره | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | رانندگان توزیع و فروشندگان | سروکنندگان غذا، غیررستورانی | رانندگان کامیون‌های سنگین و تریلی | کارمندان پذیرش هتل، متل و اقامتگاه | اپراتورهای تراکتور و کامیون صنعتی | رانندگان کامیون‌های سبک | متصدیان رختکن، اتاق لباس و اتاق پرو | ماموران اجرای مقررات پارک | متصدیان مسافران | رئیس قطارها و مدیران محوطه راه‌آهن | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | رانندگان شاتل و شوفرها | رانندگان تاکسی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | مکانیک | فروش و بازاریابی | امور اداری و مدیریت | ریاضیات | اداری</t>
+          <t>خدمات مشتری و شخصی | مکانیک | فروش و بازاریابی | مدیریت و اداره | ریاضیات | اداری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | بینایی نزدیک | زبردستی دستی | زبردستی انگشتان | دقت کنترل | قدرت تنه | تشخیص گفتار | انعطاف‌پذیری گسترده | استقامت | قدرت ایستا | هماهنگی چندعضوی | ثبات دست و بازو | ترتیب‌دهی به اطلاعات | استدلال قیاسی | بینایی دور | تجسم فضایی | حساسیت به مسئله | وضوح گفتار</t>
+          <t>بیان شفاهی | درک شفاهی | بینایی نزدیک | مهارت دستی | مهارت انگشتان | دقت کنترل | قدرت تنه | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | استقامت | قدرت ایستا | هماهنگی چند عضو | ثبات دست و بازو | ترتیب‌دهی اطلاعات | استدلال قیاسی | بینایی دور | تجسم | حساسیت به مسئله | وضوح گفتار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | صرف زمان به صورت ایستاده | در معرض آلاینده‌ها | فراوانی تصمیم‌گیری | ارتباط با دیگران | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق بودن یا صحت بالا | در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | آزادی در تصمیم‌گیری | کار با یک گروه کاری یا تیم یا مشارکت در آن | در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | صرف زمان برای پیاده‌روی یا دویدن | در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | داخل ساختمان، غیرقابل کنترل از نظر دما و رطوبت | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | پیامد اشتباه | سلامت و ایمنی سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | در معرض دماهای بسیار گرم یا سرد</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | صرف زمان برای ایستادن | قرار گرفتن در معرض آلاینده‌ها | فراوانی تصمیم‌گیری | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | پیامد خطا | سلامت و ایمنی سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | قرار گرفتن در معرض دماهای بسیار گرم یا سرد</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>متصدیان خدمات هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | تمیزکنندگان وسایل نقلیه و تجهیزات | نصاب‌ها و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | مونتاژکنندگان موتور و سایر ماشین‌آلات | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | تعمیرکاران لوازم خانگی | کارگران نگهداری ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتور | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مکانیک‌های تجهیزات برقی فضای باز و سایر موتورهای کوچک | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و سنجش‌گران | اپراتورهای پمپ، به جز پمپ‌چی‌های سر چاه | تعمیرکاران واگن‌های ریلی | کارگران ساده نفت و گاز | اپراتورهای واحد خدمات، نفت و گاز | مهندسان تاسیسات و اپراتورهای دیگ بخار | تعمیرکاران و تعویض‌کنندگان لاستیک</t>
+          <t>متصدیان خدمات هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | تمیزکنندگان وسایل نقلیه و تجهیزات | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکاران موتور و سایر ماشین‌آلات | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | تعمیرکاران لوازم خانگی | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | تعمیرکنندگان واگن‌های ریلی | کارگران فنی همه‌کاره نفت و گاز | اپراتورهای واحد خدمات، نفت و گاز | مهندسان تاسیسات و اپراتورهای دیگ بخار | تعمیرکنندگان و تعویض‌کنندگان لاستیک</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Access Software AIRPAX | مدیریت کامپیوتری دفترچه ثبت هواپیما CALM | نرم‌افزار آنالیز موتور | پایگاه‌های داده اطلاعات نگهداری | نرم‌افزار برنامه‌ریزی نگهداری | نرم‌افزار ثبت سوابق نگهداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Windows | Microsoft Word | نرم‌افزار سیستم تامین | نرم‌افزار پایگاه داده کتابچه راهنمای فنی</t>
+          <t>Access Software AIRPAX | Computerized aircraft log manager CALM | Engine analysis software | Maintenance information databases | Maintenance planning software | نرم‌افزار ثبت تعمیر و نگهداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Windows | Microsoft Word | Supply system software | Technical manual database software</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ترابری | امنیت و ایمنی عمومی | مکانیک | زبان انگلیسی | شیمی | خدمات مشتریان و شخصی | ریاضیات</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | مکانیک | زبان انگلیسی | شیمی | خدمات مشتری و شخصی | ریاضیات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>زبردستی دستی | زبردستی انگشتان | ثبات دست و بازو | هماهنگی چندعضوی | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری گسترده | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی | توجه شنیداری</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی | توجه شنیداری</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>فضای باز, در معرض تمام شرایط آب و هوایی | در معرض دماهای بسیار گرم یا سرد | در معرض آلاینده‌ها | در معرض شرایط خطرناک | در معرض تجهیزات خطرناک | در معرض صداها، سطوح نویز مزاحم یا آزاردهنده | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان به صورت ایستاده | صرف زمان برای پیاده‌روی یا دویدن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | درون یک وسیله نقلیه روباز یا کار با تجهیزات روباز | پیامد اشتباه | اهمیت دقیق بودن یا صحت بالا | سلامت و ایمنی سایر کارکنان | فشار زمانی | کار با یک گروه کاری یا تیم یا مشارکت در آن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | اهمیت تکرار وظایف یکسان</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در یک وسیله نقلیه روباز یا کار با تجهیزات | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان هوافضا | سرپرستان جابجایی بار هواپیما | مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان سازه، سطوح، ریگینگ و سیستم‌های هواپیما | خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | متصدیان خدمات خودرو و شناورهای آبی | تکنسین‌های اویونیک | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | تمیزکنندگان وسایل نقلیه و تجهیزات | خلبانان تجاری | تکنولوژیست‌ها و تکنسین‌های الکترومکانیک و مکاترونیک | کارگران نگهداری بزرگراه | اپراتورهای تراکتور و لیفتراک صنعتی | کارگران نگهداری ماشین‌آلات | کارگران نگهداری و تعمیرات، عمومی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتور | تعمیرکاران واگن‌های ریلی | مهندسان کشتی | مهندسان تاسیسات و اپراتورهای دیگ بخار</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان هوافضا | سرپرستان جابجایی بار هواپیما | مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | متصدیان خدمات خودرو و شناورهای آبی | تکنسین‌های هوانوردی | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | تمیزکنندگان وسایل نقلیه و تجهیزات | خلبانان تجاری | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | کارگران نگهداری بزرگراه‌ها | اپراتورهای تراکتور و کامیون صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران نگهداری و تعمیرات عمومی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | تعمیرکنندگان واگن‌های ریلی | مهندسان کشتی | مهندسان تاسیسات و اپراتورهای دیگ بخار</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | Bentley MicroStation | C++ | نرم‌افزار طراحی و ترسیم به کمک کامپیوتر CADD | Dowling Associates TRAFFIX | نرم‌افزار ESRI ArcGIS | ESRI ArcView | سیستم‌های سیستم اطلاعات جغرافیایی GIS | JAMAR Technologies PETRAPro | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Oracle Database | Pd' Programming Intersection Magic | Python | R | SAS | نرم‌افزار Salesforce | زبان پرس‌وجوی ساختاریافته SQL | Tableau | The MathWorks MATLAB | نرم‌افزار کنترل ترافیک | نرم‌افزار سیگنال ترافیک | Trafficware SimTraffic</t>
+          <t>Autodesk AutoCAD | Bentley MicroStation | C++ | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Dowling Associates TRAFFIX | نرم‌افزار ESRI ArcGIS | ESRI ArcView | سیستم‌های سیستم اطلاعات جغرافیایی GIS | JAMAR Technologies PETRAPro | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Oracle Database | Pd' Programming Intersection Magic | Python | R | SAS | نرم‌افزار Salesforce | زبان پرس‌وجوی ساختاریافته SQL | Tableau | The MathWorks MATLAB | نرم‌افزار کنترل ترافیک | نرم‌افزار سیگنال ترافیک | Trafficware SimTraffic</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | مانیتورینگ | یادگیری فعال</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>امنیت و ایمنی عمومی | ترابری | کامپیوتر و الکترونیک | زبان انگلیسی | مهندسی و فناوری | قانون و دولت | ریاضیات | خدمات مشتریان و شخصی | اداری | آموزش و تربیت | مکانیک | طراحی | ساختمان و ساخت‌وساز</t>
+          <t>ایمنی و امنیت عمومی | حمل و نقل | رایانه و الکترونیک | زبان انگلیسی | مهندسی و فناوری | قانون و دولت | ریاضیات | خدمات مشتری و شخصی | اداری | آموزش و پرورش | مکانیک | طراحی | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | درک کتبی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | تجسم فضایی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی به اطلاعات | بیان کتبی | استدلال ریاضی | اصالت | روان بودن ایده‌ها | سهولت در کار با اعداد</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | درک کتبی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان کتبی | استدلال ریاضی | اصالت | روانی ایده‌ها | توانایی عددی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | اهمیت دقیق بودن یا صحت بالا | درون یک وسیله نقلیه محصور یا کار با تجهیزات محصور | داخل ساختمان، کنترل‌شده از نظر دما و رطوبت | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | مکالمات تلفنی | کار با یک گروه کاری یا تیم یا مشارکت در آن | آزادی در تصمیم‌گیری | فضای باز، در معرض تمام شرایط آب و هوایی | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | ارتباط با دیگران | اهمیت تکرار وظایف یکسان | تاثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | در معرض تجهیزات خطرناک | صرف زمان به صورت نشسته</t>
+          <t>ایمیل | اهمیت دقیق یا درست بودن | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | فضای باز، در معرض تمام شرایط آب و هوایی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | ارتباط با دیگران | اهمیت تکرار وظایف یکسان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کنترل‌کنندگان ترافیک هوایی | بازرسان هوانوردی | تکنولوژیست‌ها و تکنسین‌های مهندسی عمران | مهندسان عمران | بازرسان ساخت‌وساز و ساختمان | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | سرپرستان خط اول اپراتورهای ماشین‌آلات جابجایی مواد و وسایل نقلیه | نقشه برداران ژئودتیک | کارگران نگهداری بزرگراه | مهندسان لوکوموتیو | مهندسان لجستیک | توزیع‌کنندگان و دیسپچرهای برق | لوکوموتیورانان و روسای ایستگاه راه‌آهن | تعمیرکاران سیگنال و سوزن ریل | تکنسین‌های نقشه برداری و نقشه‌کشی | مهندسان حمل‌ونقل | بازرسان حمل‌ونقل | برنامه‌ریزان حمل‌ونقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>کنترلرهای ترافیک هوایی | بازرسان هوانوردی | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان عمران | بازرسان ساختمان و ساخت‌وساز | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | نقشه‌برداران ژئودتیک | کارگران نگهداری بزرگراه‌ها | مهندسان لوکوموتیو | مهندسان لجستیک | توزیع‌کنندگان و دیسپچرهای برق | رئیس قطارها و مدیران محوطه راه‌آهن | تعمیرکاران سیگنال و سوزن ریل | تکنسین‌های نقشه‌برداری و نقشه‌کشی | مهندسان حمل و نقل | بازرسان حمل‌ونقل | برنامه‌ریزان حمل‌ونقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | گوش دادن فعال | مانیتورینگ</t>
+          <t>تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | گوش دادن فعال | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ترابری | زبان انگلیسی | خدمات مشتریان و شخصی | ریاضیات | امنیت و ایمنی عمومی | امور اداری و مدیریت | مکانیک | قانون و دولت</t>
+          <t>حمل و نقل | زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | ایمنی و امنیت عمومی | مدیریت و اداره | مکانیک | قانون و دولت</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | درک کتبی | بیان کتبی | استدلال استقرایی | ترتیب‌دهی به اطلاعات | تشخیص گفتار | بینایی دور | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | تجسم فضایی | سرعت ادراکی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | درک کتبی | بیان کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | تشخیص گفتار | بینایی دور | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | اهمیت دقیق بودن یا صحت بالا | ایمیل | تعیین وظایف, اولویت‌ها و اهداف | ارتباط با دیگران | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فضای باز، در معرض تمام شرایط آب و هوایی | فراوانی تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | درون یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فشار زمانی | در معرض صداها، سطوح نویز مزاحم یا آزاردهنده | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | پیامدهای کاری و نتایج سایر کارکنان | داخل ساختمان، غیرقابل کنترل از نظر دما و رطوبت | نامه‌ها و یادداشت‌های مکتوب | در معرض آلاینده‌ها</t>
+          <t>مکالمات تلفنی | اهمیت دقیق یا درست بودن | ایمیل | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فضای باز، در معرض تمام شرایط آب و هوایی | فراوانی تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فشار زمانی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تعامل با مشتریان خارجی یا عموم مردم | پیامدهای کاری و نتایج سایر کارکنان | محیط داخلی، بدون کنترل شرایط محیطی | نامه‌ها و یادداشت‌های کتبی | قرار گرفتن در معرض آلاینده‌ها</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی | سرپرستان جابجایی بار هواپیما | متخصصان عملیات فرودگاه | بازرسان هوانوردی | ماموران بار و محموله | بازرسان ساخت‌وساز و ساختمان | سرپرستان خط اول کمک‌کاران، کارگران ساده و جابجاکنندگان دستی مواد | سرپرستان خط اول اپراتورهای ماشین‌آلات جابجایی مواد و وسایل نقلیه | متصدیان ارسال کالا (فورواردینگ) | بازرسان و محققان اموال دولتی | بازرسان، تست‌کنندگان، سورترها، نمونه‌گیران و توزین‌کنندگان | مهندسان لوکوموتیو | مهندسان دریایی و معماران نیروی دریایی | متخصصان بهداشت و ایمنی شغلی | لوکوموتیورانان و روسای ایستگاه راه‌آهن | مهندسان کشتی | کارمندان ارسال، دریافت و موجودی کالا | بارگیران واگن‌های مخزنی، کامیون‌ها و کشتی‌ها | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>بازرسان کشاورزی | سرپرستان جابجایی بار هواپیما | متخصصان عملیات فرودگاه | بازرسان هوانوردی | نمایندگان بار و محموله | بازرسان ساختمان و ساخت‌وساز | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | متصدیان حمل و نقل | بازرسان و محققان اموال دولتی | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | مهندسان لوکوموتیو | مهندسان دریایی و معماران کشتی | متخصصان بهداشت و ایمنی شغلی | رئیس قطارها و مدیران محوطه راه‌آهن | مهندسان کشتی | کارمندان ارسال، دریافت و موجودی کالا | بارگیران واگن مخزنی، کامیون و کشتی | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | مانیتورینگ | یادگیری فعال</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | مکانیک | امنیت و ایمنی عمومی | خدمات مشتریان و شخصی | ترابری | آموزش و تربیت | تولید و فرآوری | مهندسی و فناوری | ریاضیات | امور اداری و مدیریت | قانون و دولت | کامپیوتر و الکترونیک | طراحی | فیزیک | اداری | مخابرات</t>
+          <t>زبان انگلیسی | مکانیک | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | حمل و نقل | آموزش و پرورش | تولید و فرآوری | مهندسی و فناوری | ریاضیات | مدیریت و اداره | قانون و دولت | رایانه و الکترونیک | طراحی | فیزیک | اداری | مخابرات</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | حساسیت به مسئله | درک شفاهی | استدلال قیاسی | بینایی نزدیک | درک کتبی | بیان شفاهی | وضوح گفتار | بیان کتبی | تشخیص گفتار | ترتیب‌دهی به اطلاعات | بینایی دور | تجسم فضایی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | توجه شنیداری | حساسیت شنوایی | تشخیص رنگ‌های بصری | دقت کنترل | زبردستی دستی | ثبات دست و بازو | اشتراک زمانی | روان بودن ایده‌ها</t>
+          <t>استدلال استقرایی | حساسیت به مسئله | درک شفاهی | استدلال قیاسی | بینایی نزدیک | درک کتبی | بیان شفاهی | وضوح گفتار | بیان کتبی | تشخیص گفتار | ترتیب‌دهی اطلاعات | بینایی دور | تجسم | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | توجه شنیداری | حساسیت شنوایی | تشخیص رنگ بصری | دقت کنترل | مهارت دستی | ثبات دست و بازو | تقسیم توجه | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | پیامد اشتباه | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق بودن یا صحت بالا | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | کار با یک گروه کاری یا تیم یا مشارکت در آن | فشار زمانی | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | در معرض صداها، سطوح نویز مزاحم یا آزاردهنده | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک, دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | داخل ساختمان، کنترل‌شده از نظر دما و رطوبت | در معرض دماهای بسیار گرم یا سرد | در معرض آلاینده‌ها | داخل ساختمان، غیرقابل کنترل از نظر دما و رطوبت | در معرض فضای کاری تنگ، موقعیت‌های نامناسب بدنی | نامه‌ها و یادداشت‌های مکت | سطح رقابت | فضای باز، در معرض تمام شرایط آب و هوایی | در معرض شرایط نوری بسیار روشن یا ناکافی | صرف زمان به صورت ایستاده</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | محیط داخلی، دارای کنترل شرایط محیطی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض آلاینده‌ها | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | نامه‌ها و یادداشت‌های کتبی | سطح رقابت | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | صرف زمان برای ایستادن</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان هوافضا | مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان سازه، سطوح، ریگینگ و سیستم‌های هواپیما | متخصصان عملیات فرودگاه | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک | خلبانان تجاری | بازرسان ساخت‌وساز و ساختمان | نصاب‌ها و تعمیرکاران برق و الکترونیک، تجهیزات حمل‌ونقل | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | بازرسان و محققان اموال دولتی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | مهندسان صنایع | بازرسان، تست‌کنندگان، سورترها، نمونه‌گیران و توزین‌کنندگان | مهندسان لوکوموتیو | متخصصان بهداشت و ایمنی شغلی | مهندسان کشتی | بازرسان حمل‌ونقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان هوافضا | مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | متخصصان عملیات فرودگاه | تکنسین‌های مهندسی خودرو | تکنسین‌های هوانوردی | خلبانان تجاری | بازرسان ساختمان و ساخت‌وساز | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | بازرسان و محققان اموال دولتی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | مهندسان صنایع | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | مهندسان لوکوموتیو | متخصصان بهداشت و ایمنی شغلی | مهندسان کشتی | بازرسان حمل‌ونقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>دستورالعمل‌های نگهداری | تفکر انتقادی | سخن گفتن | درک مطلب</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مکانیک | ترابری | زبان انگلیسی | امنیت و ایمنی عمومی</t>
+          <t>مکانیک | حمل و نقل | زبان انگلیسی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | فراوانی تصمیم‌گیری | در معرض صداها، سطوح نویز مزاحم یا آزاردهنده | صرف زمان به صورت ایستاده | تاثیر تصمیمات بر همکاران یا نتایج شرکت | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق بودن یا صحت بالا | فشار زمانی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | پیامد اشتباه | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یک گروه کاری یا تیم یا مشارکت در آن | در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | داخل ساختمان، غیرقابل کنترل از نظر دما و رطوبت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای پیاده‌روی یا دویدن | سلامت و ایمنی سایر کارکنان | در معرض آلاینده‌ها | در معرض شرایط خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | مکالمات تلفنی | درون یک وسیله نقلیه محصور یا کار با تجهیزات محصور | سطح رقابت</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | فراوانی تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای ایستادن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | فشار زمانی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | پیامد خطا | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | محیط داخلی، بدون کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای راه رفتن یا دویدن | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض شرایط خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | مکالمات تلفنی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | سطح رقابت</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی و عملیات هوافضا | مکانیک‌ها و تکنسین‌های خدمات هواپیما | تکنسین‌های مهندسی خودرو | تکنسین‌ها و مکانیک‌های خدمات خودرو | بازرسان هوانوردی | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | بازرسان ساخت‌وساز و ساختمان | نصاب‌ها و تعمیرکاران برق و الکترونیک، تجهیزات حمل‌ونقل | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | بازرسان، تست‌کنندگان، سورترها، نمونه‌گیران و توزین‌کنندگان | مهندسان لوکوموتیو | کارگران نگهداری و تعمیرات، عمومی | متخصصان بهداشت و ایمنی شغلی | تعمیرکاران واگن‌های ریلی | لوکوموتیورانان و روسای ایستگاه راه‌آهن | مهندسان کشتی | مهندسان تاسیسات و اپراتورهای دیگ بخار | بازرسان حمل‌ونقل</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مکانیک‌ها و تکنسین‌های خدمات هواپیما | تکنسین‌های مهندسی خودرو | تکنسین‌ها و مکانیک‌های خدمات خودرو | بازرسان هوانوردی | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | بازرسان ساختمان و ساخت‌وساز | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | مهندسان لوکوموتیو | کارگران نگهداری و تعمیرات عمومی | متخصصان بهداشت و ایمنی شغلی | تعمیرکنندگان واگن‌های ریلی | رئیس قطارها و مدیران محوطه راه‌آهن | مهندسان کشتی | مهندسان تاسیسات و اپراتورهای دیگ بخار | بازرسان حمل‌ونقل</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | مانیتورینگ | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ترابری | زبان انگلیسی | امنیت و ایمنی عمومی | خدمات مشتریان و شخصی</t>
+          <t>حمل و نقل | زبان انگلیسی | ایمنی و امنیت عمومی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>نزدیکی فیزیکی | ارتباط با دیگران | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | در معرض دماهای بسیار گرم یا سرد | صرف زمان به صورت نشسته | فراوانی تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | در معرض آلاینده‌ها</t>
+          <t>نزدیکی فیزیکی | ارتباط با دیگران | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای نشستن | فراوانی تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>سرپرستان جابجایی بار هواپیما | متخصصان عملیات فرودگاه | باربران چمدان و پادوهای هتل | رانندگان اتوبوس، ترانزیت و بین‌شهری | دربانان هتل (کانسیرج) | دیسپچرها، به جز پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط اول متصدیان مسافران | مهمانداران هواپیما | میزبانان رستوران، سالن و کافی‌شاپ | متصدیان پذیرش هتل، متل و اقامتگاه | متصدیان رختکن و اتاق پرو | بهیاران | متصدیان پارکینگ | لوکوموتیورانان و روسای ایستگاه راه‌آهن | ماموران فروش بلیط رزرو و حمل‌ونقل و کارمندان سفر | مراقبان اتوبوس مدرسه | رانندگان شاتل و شوفرها | اپراتورهای مترو و تراموا | رانندگان تاکسی | راهنمایان سالن، متصدیان لابی و بلیط‌گیرها</t>
+          <t>سرپرستان جابجایی بار هواپیما | متخصصان عملیات فرودگاه | باربران چمدان و پادوهای هتل | رانندگان اتوبوس، ترانزیت و بین‌شهری | کانسرج‌ها | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط اول مهمانداران مسافری | مهمانداران هواپیما | میزبانان رستوران، سالن و کافی‌شاپ | کارمندان پذیرش هتل، متل و اقامتگاه | متصدیان رختکن، اتاق لباس و اتاق پرو | بهیاران | متصدیان پارکینگ | رئیس قطارها و مدیران محوطه راه‌آهن | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | مراقبین اتوبوس مدرسه | رانندگان شاتل و شوفرها | رانندگان مترو و تراموا | رانندگان تاکسی | راهنماها، متصدیان لابی و بلیط‌گیرها</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>نرم‌افزار مدیریت ناوگان | نرم‌افزار مدیریت حمل‌ونقل | سیستم مدیریت انبار WMS | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | سیستم‌های مدیریت موجودی | نرم‌افزار پایگاه داده | نرم‌افزار برنامه‌ریزی | نرم‌افزار مرورگر وب | Microsoft Outlook | سیستم برنامه‌ریزی منابع سازمانی ERP</t>
+          <t>نرم‌افزار مدیریت ناوگان | نرم‌افزار مدیریت حمل و نقل | سیستم مدیریت انبار WMS | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | سیستم‌های مدیریت موجودی | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | نرم‌افزار مرورگر وب | Microsoft Outlook | سیستم برنامه‌ریزی منابع سازمانی ERP</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ترابری | امنیت و ایمنی عمومی | خدمات مشتریان و شخصی | زبان انگلیسی | مکانیک | جغرافیا</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | زبان انگلیسی | مکانیک | جغرافیا</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>زبردستی دستی | زبردستی انگشتان | ثبات دست و بازو | هماهنگی چندعضوی | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری گسترده | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض دماهای بسیار گرم یا سرد | در معرض آلاینده‌ها | در معرض تجهیزات خطرناک | در معرض صداها، سطوح نویز مزاحم یا آزاردهنده | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | در معرض ارتفاعات بالا | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی | ارتباط با دیگران | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | فشار زمانی | مکالمات تلفنی | درون یک وسیله نقلیه محصور یا کار با تجهیزات محصور</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | قرار گرفتن در معرض ارتفاعات بالا | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی | مکالمات تلفنی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متصدیان خدمات هواپیما | متصدیان پارکینگ | متصدیان خدمات خودرو و شناورهای آبی | متصدیان مسافران | متصدیان پل و کانال | تکنسین‌های ترافیک | بازرسان حمل‌ونقل | بازرسان هوانوردی | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی | متخصصان عملیات فرودگاه | مهمانداران هواپیما | اپراتورهای تراکتور و لیفتراک صنعتی | کارگران ساده و جابجاکنندگان دستی بار، کالا و مواد | تمیزکنندگان وسایل نقلیه و تجهیزات | ماموران بار و محموله | دیسپچرها، به جز پلیس، آتش‌نشانی و آمبولانس | رانندگان کامیونت | سرپرستان خط اول کارگران حمل‌ونقل، سایر | سرپرستان خط اول متصدیان مسافران | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>متصدیان خدمات هواپیما | متصدیان پارکینگ | متصدیان خدمات خودرو و شناورهای آبی | متصدیان مسافران | متصدیان پل و کانال | تکنسین‌های ترافیک | بازرسان حمل‌ونقل | بازرسان هوانوردی | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی | متخصصان عملیات فرودگاه | مهمانداران هواپیما | اپراتورهای تراکتور و کامیون صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | تمیزکنندگان وسایل نقلیه و تجهیزات | نمایندگان بار و محموله | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | رانندگان کامیون‌های سبک | سرپرستان خط اول کارگران حمل و نقل، سایر | سرپرستان خط اول مهمانداران مسافری | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0098_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0098_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>مرتب‌سازی اطلاعات | دید نزدیک | توجه شنیداری | دید دور | دقت کنترل | توجه انتخابی | وضوح گفتار | تشخیص گفتار | حساسیت شنوایی | زمان واکنش | ثبات دست و بازو | سرعت ادراک | حساسیت به مسئله | بیان شفاهی | درک شفاهی</t>
+          <t>ترتیب‌دهی اطلاعات | بینایی نزدیک | توجه شنیداری | بینایی دور | دقت کنترل | توجه انتخابی | وضوح گفتار | تشخیص گفتار | حساسیت شنوایی | زمان عکس‌العمل | ثبات دست و بازو | سرعت ادراکی | حساسیت به مسئله | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ناخداها، افسران اول و راهنمایان شناورهای دریایی | اپراتورهای جرثقیل و دکل | اپراتورهای لایروب | نصابان و تعمیرکاران خطوط انتقال برق | کارگران نگهداری و مرمت بزرگراه‌ها | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و لیفتراک‌های صنعتی | قفل‌سازان و تعمیرکاران گاوصندوق | لکوموتیورانان | هدایت‌کنندگان قایق‌های موتوری | مهندسان بهره‌برداری و اپراتورهای ماشین‌آلات سنگین عمرانی | مهندسان، اپراتورهای مانور و سوزن‌بانان محوطه راه‌آهن | ترمزبانان، پرچم‌داران و متصدیان خطوط راه‌آهن و آتش‌کاران لکوموتیو | رئیسان قطار و سرپرستان ایستگاه راه‌آهن | ریگرها و سیم‌بکسل‌اندازان | ملوانان و روغن‌کاران موتورخانه شناورها | نگهبانان و ماموران حراست | مهندسان کشتی | تعمیرکاران علائم و سوزن‌های خطوط راه‌آهن | بارگیران مخزن‌دارها، تانکرها و شناورها</t>
+          <t>کاپیتان‌ها، افسران اول و راهنمایان شناورهای دریایی | اپراتورهای جرثقیل و تاورکرین | اپراتورهای لایروب | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | کارگران راهداری و نگهداری جاده‌ها | اپراتورهای بالابر و وینچ | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | قفل‌سازان و تعمیرکاران گاوصندوق | لکوموتیورانان | قایقرانان قایق‌های موتوری | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رؤسای قطار و مدیران محوطه راه‌آهن | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | ملوانان و روغن‌کاران شناورهای دریایی | نگهبانان و ماموران حراست | مهندسان فنی کشتی | تعمیرکاران علائم، سیگنال‌ها و سوزن‌های راه‌آهن | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال</t>
+          <t>سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ترابری و حمل‌ونقل</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | حمل و نقل</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دید دور | درک شفاهی | بیان شفاهی | تشخیص گفتار | دید نزدیک | وضوح گفتار | حساسیت به مسئله | جهت‌یابی فضایی | استدلال استقرایی | استدلال قیاسی | دقت کنترل | توجه انتخابی | مرتب‌سازی اطلاعات | ادراک عمق | هماهنگی اندام‌ها</t>
+          <t>بینایی دور | درک شفاهی | بیان شفاهی | تشخیص گفتار | بینایی نزدیک | وضوح گفتار | حساسیت به مسئله | جهت‌گیری فضایی | استدلال استقرایی | استدلال قیاسی | دقت کنترل | توجه انتخابی | ترتیب‌دهی اطلاعات | درک عمق | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>متصدیان اماکن تفریحی و گردشگری | باربران هتل و چمدان‌بران | رانندگان اتوبوس‌های شهری و بین‌شهری | صندوق‌داران | راهنمایان پذیرش و خدمات هتل (کانسیرژ) | متصدیان باجه و کرایه تجهیزات | اعزام‌کنندگان و دیسپچرهای ترابری (به‌جز پلیس، آتش‌نشانی و اورژانس) | رانندگان توزیع و فروش | مهمانداران و سالن‌داران خارج از رستوران | رانندگان تریلر و کامیون‌های سنگین | متصدیان پذیرش هتل و متل | اپراتورهای تراکتور و لیفتراک‌های صنعتی | رانندگان کامیونت و وانت‌بار | متصدیان رختکن و اتاق‌های تعویض لباس | ماموران اعمال قانون و نظارت بر پارکینگ‌ها | متصدیان خدمات مسافران | رئیسان قطار و سرپرستان ایستگاه راه‌آهن | متصدیان فروش و رزرو بلیت و خدمات سفر | رانندگان سرویس و تشریفات | رانندگان تاکسی</t>
+          <t>متصدیان اماکن تفریحی و شهربازی | متصدیان حمل بار و خدمات هتل | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | صندوق‌داران | متصدیان تشریفات و خدمات میهمانان | متصدیان باجه و کرایه کالا و خدمات | متصدیان دیسپاچ و اعزام | رانندگان توزیع و فروش مویرگی | سروکنندگان غذا در محیط‌های غیررستورانی | رانندگان خودروهای سنگین و کشنده‌ها | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | رانندگان خودروهای باربری سبک و وانت‌بارها | متصدیان رختکن، امانات و اتاق پرو | ماموران کنترل و اعمال قانون پارک دوبله و توقف | مهمانداران و متصدیان خدمات مسافران | رؤسای قطار و مدیران محوطه راه‌آهن | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | رانندگان خودروهای سرویس و تشریفات | رانندگان تاکسی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مکانیک | بازاریابی و فروش | مدیریت و امور اداری | ریاضیات | امور اداری و دفتری</t>
+          <t>خدمات مشتری و شخصی | مکانیک | فروش و بازاریابی | مدیریت و اداره | ریاضیات | اداری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | دید نزدیک | چابکی دستی | چابکی انگشتان | دقت کنترل | استحکام بالاتنه | تشخیص گفتار | انعطاف‌پذیری دامنه حرکتی | استقامت بدنی | قدرت ایستا | هماهنگی اندام‌ها | ثبات دست و بازو | مرتب‌سازی اطلاعات | استدلال قیاسی | دید دور | تجسم فضایی | حساسیت به مسئله | وضوح گفتار</t>
+          <t>بیان شفاهی | درک شفاهی | بینایی نزدیک | مهارت دستی | مهارت انگشتان | دقت کنترل | قدرت تنه | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | استقامت | قدرت ایستا | هماهنگی چند عضو | ثبات دست و بازو | ترتیب‌دهی اطلاعات | استدلال قیاسی | بینایی دور | تجسم | حساسیت به مسئله | وضوح گفتار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>متصدیان خدمات و سوخت‌رسانی فرودگاهی | تکنسین‌ها و مکانیک‌های خدمات خودرویی | مکانیک‌های اتوبوس، کامیون و متخصصان موتورهای دیزلی | کارگران شست‌وشوی وسایل نقلیه و تجهیزات | نصابان و تعمیرکاران شیرآلات و تجهیزات کنترلی صنعتی | تعمیرکاران الکتروموتورها، ابزارهای برقی و ادوات مرتبط | مونتاژکاران موتور و ماشین‌آلات | اپراتورهای کمپرسور گاز و ایستگاه‌های پمپاژ گاز | تعمیرکاران لوازم خانگی | کارگران نگهداری و تعمیرات ماشین‌آلات صنعتی | مکانیک‌های ماشین‌آلات سنگین متحرک عمرانی | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مکانیک‌های تجهیزات موتوری فضای سبز و موتورهای کوچک | اپراتورهای سامانه‌های پمپاژ نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای پمپ‌های صنعتی (به‌جز سرچاهی) | تعمیرکاران واگن‌های راه‌آهن | کارگران ساده و حفاری نفت و گاز | اپراتورهای واحدهای خدمات سرچاهی نفت و گاز | مهندسان تاسیسات و اپراتورهای بویلرها و دیگ‌های بخار | آپاراتی‌ها و تعمیرکاران و تعویض‌کنندگان لاستیک</t>
+          <t>متصدیان خدمات زمینی و سوخت‌رسانی فرودگاهی | مکانیک و تکنسین خدمات خودرو | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران موتور و سایر ماشین‌آلات | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | تعمیرکاران لوازم خانگی | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک تجهیزات سنگین متحرک | مکانیک و تکنسین شناورهای موتوری | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | تعمیرکار واگن قطار | کارگران عمومی سکو و میادین نفت و گاز | اپراتورهای واحدهای خدمات چاه نفت و گاز | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | آپاراتی و پنچرگیر و تعویض‌کار لاستیک</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ترابری و حمل‌ونقل | ایمنی و امنیت عمومی | مکانیک | زبان انگلیسی | شیمی | خدمات مشتریان و خدمات فردی | ریاضیات</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | مکانیک | زبان انگلیسی | شیمی | خدمات مشتری و شخصی | ریاضیات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی اندام‌ها | دقت کنترل | قدرت ایستا | استحکام بالاتنه | استقامت بدنی | دید نزدیک | دید دور | ادراک عمق | هماهنگی عمومی بدن | تعادل عمومی بدن | انعطاف‌پذیری دامنه حرکتی | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی | توجه شنیداری</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی | توجه شنیداری</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی هوافضا و عملیات هوانوردی | مهندسان هوافضا | سرپرستان جابه‌جایی بار و بارگیری هواپیما | تکنسین‌ها و مکانیک‌های هواپیما | مونتاژکاران سازه، سطوح و سامانه‌های هوانوردی | خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | متصدیان جایگاه‌های سوخت و خدمات وسایل نقلیه و شناورها | تکنسین‌های اویونیک و الکترونیک هواپیما | مکانیک‌های اتوبوس، کامیون و متخصصان موتورهای دیزلی | کارگران شست‌وشوی وسایل نقلیه و تجهیزات | خلبانان تجاری | کاردان‌ها و تکنسین‌های الکترومکانیک و مکاترونیک | کارگران نگهداری و مرمت بزرگراه‌ها | اپراتورهای تراکتور و لیفتراک‌های صنعتی | کارگران نگهداری و تعمیرات ماشین‌آلات صنعتی | کارگران تعمیرات و نگهداری عمومی تاسیسات | مکانیک‌های ماشین‌آلات سنگین متحرک عمرانی | تعمیرکاران واگن‌های راه‌آهن | مهندسان کشتی | مهندسان تاسیسات و اپراتورهای بویلرها و دیگ‌های بخار</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان هوافضا | سرپرستان بارگیری و جابه‌جایی بار هواپیما | مکانیک و تکنسین خدمات هواپیما | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | متصدیان جایگاه‌های سوخت و خدمات وسایل نقلیه و شناورها | تکنسین‌های اویونیک و الکترونیک پرواز | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | خلبانان تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | کارگران راهداری و نگهداری جاده‌ها | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران عمومی تعمیرات و نگهداری تاسیسات | مکانیک تجهیزات سنگین متحرک | تعمیرکار واگن قطار | مهندسان فنی کشتی | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | نظارت | یادگیری فعال</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | ترابری و حمل‌ونقل | رایانه و الکترونیک | زبان انگلیسی | مهندسی و فناوری | قوانین و مقررات دولتی | ریاضیات | خدمات مشتریان و خدمات فردی | امور اداری و دفتری | آموزش و تدریس | مکانیک | طراحی مهندسی | ساختمان‌سازی و سازه</t>
+          <t>ایمنی و امنیت عمومی | حمل و نقل | رایانه و الکترونیک | زبان انگلیسی | مهندسی و فناوری | قانون و دولت | ریاضیات | خدمات مشتری و شخصی | اداری | آموزش و پرورش | مکانیک | طراحی | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | درک کتبی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | دید نزدیک | دید دور | توجه انتخابی | تجسم فضایی | سرعت ادراک | انعطاف‌پذیری در بستن الگو | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | بیان کتبی | استدلال ریاضی | ابتکار و اصالت | روانی ایده‌ها | محاسبات عددی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | درک کتبی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان کتبی | استدلال ریاضی | اصالت | روانی ایده‌ها | توانایی عددی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کنترلرهای ترافیک هوایی | بازرسان هوانوردی و فرودگاهی | کاردان‌ها و تکنسین‌های مهندسی عمران | مهندسان عمران | بازرسان سازه و ساختمان | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | نقشه‌برداران ژئودتیک | کارگران نگهداری و مرمت بزرگراه‌ها | لکوموتیورانان | مهندسان لجستیک و زنجیره تامین | دیسپچرها و توزیع‌کنندگان شبکه برق | رئیسان قطار و سرپرستان ایستگاه راه‌آهن | تعمیرکاران علائم و سوزن‌های خطوط راه‌آهن | تکنسین‌های نقشه‌برداری و نقشه‌کشی | مهندسان حمل‌ونقل و ترافیک | بازرسان ترابری و حمل‌ونقل | برنامه‌ریزان حمل‌ونقل و ترافیک | بازرسان تجهیزات، سامانه‌ها و وسایل نقلیه ترابری (به‌جز هوانوردی) | مدیران ترابری، انبارداری و توزیع</t>
+          <t>کنترلرهای ترافیک هوایی | بازرسان هوانوردی و فرودگاهی | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | بازرسان ساخت‌وساز و ساختمان | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | مهندسان نقشه‌برداری ژئودزی | کارگران راهداری و نگهداری جاده‌ها | لکوموتیورانان | مهندسان لجستیک و زنجیره تأمین | دیسپچرها و توزیع‌کنندگان شبکه برق | رؤسای قطار و مدیران محوطه راه‌آهن | تعمیرکاران علائم، سیگنال‌ها و سوزن‌های راه‌آهن | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | مهندسان حمل‌ونقل و ترافیک | بازرسان ترابری و حمل‌ونقل | برنامه‌ریزان سیستم‌های حمل‌ونقل | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی) | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | شنیدن فعال | نظارت</t>
+          <t>تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | گوش دادن فعال | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ترابری و حمل‌ونقل | زبان انگلیسی | خدمات مشتریان و خدمات فردی | ریاضیات | ایمنی و امنیت عمومی | مدیریت و امور اداری | مکانیک | قوانین و مقررات دولتی</t>
+          <t>حمل و نقل | زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | ایمنی و امنیت عمومی | مدیریت و اداره | مکانیک | قانون و دولت</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | درک کتبی | بیان کتبی | استدلال استقرایی | مرتب‌سازی اطلاعات | تشخیص گفتار | دید دور | وضوح گفتار | انعطاف‌پذیری طبقه‌بندی | انعطاف‌پذیری در بستن الگو | توجه انتخابی | تجسم فضایی | سرعت ادراک</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | درک کتبی | بیان کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | تشخیص گفتار | بینایی دور | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی و قرنطینه | سرپرستان جابه‌جایی بار و بارگیری هواپیما | کارشناسان عملیات فرودگاهی | بازرسان هوانوردی و فرودگاهی | متصدیان بار و لجستیک کالا | بازرسان سازه و ساختمان | سرپرستان رده‌اول کارگران ساده و جابه‌جایی دستی بار | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | فورواردرها و متصدیان حمل‌ونقل بین‌المللی کالا | بازرسان و ممیزان اموال دولتی | بازرسان، آزمون‌گران، تفکیک‌کنندگان، نمونه‌برداران و متصدیان توزین | لکوموتیورانان | مهندسان دریایی و معماران کشتی | کارشناسان ایمنی و بهداشت حرفه‌ای | رئیسان قطار و سرپرستان ایستگاه راه‌آهن | مهندسان کشتی | کارمندان امور ارسال، دریافت و انبارداری | بارگیران مخزن‌دارها، تانکرها و شناورها | بازرسان تجهیزات، سامانه‌ها و وسایل نقلیه ترابری (به‌جز هوانوردی) | مدیران ترابری، انبارداری و توزیع</t>
+          <t>بازرسان محصولات و فرآورده‌های کشاورزی | سرپرستان بارگیری و جابه‌جایی بار هواپیما | کارشناسان عملیات فرودگاهی | بازرسان هوانوردی و فرودگاهی | کارگزاران حمل‌ونقل و بار | بازرسان ساخت‌وساز و ساختمان | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | بازرسان و ممیزان اموال دولتی | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | لکوموتیورانان | مهندسان دریایی و معماران کشتی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | رؤسای قطار و مدیران محوطه راه‌آهن | مهندسان فنی کشتی | کارمندان انبار، ارسال و دریافت کالا | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی) | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | مکانیک | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | ترابری و حمل‌ونقل | آموزش و تدریس | تولید و فرآوری | مهندسی و فناوری | ریاضیات | مدیریت و امور اداری | قوانین و مقررات دولتی | رایانه و الکترونیک | طراحی مهندسی | فیزیک | امور اداری و دفتری | مخابرات</t>
+          <t>زبان انگلیسی | مکانیک | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | حمل و نقل | آموزش و پرورش | تولید و فرآوری | مهندسی و فناوری | ریاضیات | مدیریت و اداره | قانون و دولت | رایانه و الکترونیک | طراحی | فیزیک | اداری | مخابرات</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | حساسیت به مسئله | درک شفاهی | استدلال قیاسی | دید نزدیک | درک کتبی | بیان شفاهی | وضوح گفتار | بیان کتبی | تشخیص گفتار | مرتب‌سازی اطلاعات | دید دور | تجسم فضایی | سرعت ادراک | انعطاف‌پذیری طبقه‌بندی | انعطاف‌پذیری در بستن الگو | توجه انتخابی | توجه شنیداری | حساسیت شنوایی | تمایز رنگ‌ها | دقت کنترل | چابکی دستی | ثبات دست و بازو | تقسیم توجه | روانی ایده‌ها</t>
+          <t>استدلال استقرایی | حساسیت به مسئله | درک شفاهی | استدلال قیاسی | بینایی نزدیک | درک کتبی | بیان شفاهی | وضوح گفتار | بیان کتبی | تشخیص گفتار | ترتیب‌دهی اطلاعات | بینایی دور | تجسم | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | توجه شنیداری | حساسیت شنوایی | تشخیص رنگ بصری | دقت کنترل | مهارت دستی | ثبات دست و بازو | تقسیم توجه | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>اهمیت بسیار بالای دقت و عدم پذیرش خطا | پیامدهای سنگین ناشی از اشتباه بر ایمنی عمومی | تصمیم‌گیری‌های حساس و قضاوت‌های مستقل | استفاده از تجهیزات حفاظت فردی | مکاتبهٔ ایمیلی | گفت‌وگوی حضوری با همکاران | مواجهه با صداهای با دسی‌بل بالا</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | محیط داخلی، دارای کنترل شرایط محیطی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض آلاینده‌ها | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | نامه‌ها و یادداشت‌های کتبی | سطح رقابت | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | صرف زمان برای ایستادن</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی هوافضا و عملیات هوانوردی | مهندسان هوافضا | تکنسین‌ها و مکانیک‌های هواپیما | مونتاژکاران سازه، سطوح و سامانه‌های هوانوردی | کارشناسان عملیات فرودگاهی | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک و الکترونیک هواپیما | خلبانان تجاری | بازرسان سازه و ساختمان | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی ناوگان ترابری | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | بازرسان و ممیزان اموال دولتی | مهندسان ایمنی و بهداشت حرفه‌ای (به‌جز مهندسان و بازرسان ایمنی معدن) | مهندسان صنایع | بازرسان، آزمون‌گران، تفکیک‌کنندگان، نمونه‌برداران و متصدیان توزین | لکوموتیورانان | کارشناسان ایمنی و بهداشت حرفه‌ای | مهندسان کشتی | بازرسان ترابری و حمل‌ونقل | بازرسان تجهیزات، سامانه‌ها و وسایل نقلیه ترابری (به‌جز هوانوردی)</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان هوافضا | مکانیک و تکنسین خدمات هواپیما | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | کارشناسان عملیات فرودگاهی | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک و الکترونیک پرواز | خلبانان تجاری | بازرسان ساخت‌وساز و ساختمان | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | بازرسان و ممیزان اموال دولتی | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | مهندسان صنایع | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | لکوموتیورانان | کارشناسان بهداشت حرفه‌ای و ایمنی کار | مهندسان فنی کشتی | بازرسان ترابری و حمل‌ونقل | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مکانیک | ترابری و حمل‌ونقل | زبان انگلیسی | ایمنی و امنیت عمومی</t>
+          <t>مکانیک | حمل و نقل | زبان انگلیسی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | درک شفاهی | ثبات دست و بازو | انعطاف‌پذیری در بستن الگو | استدلال قیاسی | بیان شفاهی | وضوح گفتار | توجه شنیداری | حساسیت شنوایی | توجه انتخابی | استدلال استقرایی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | درک شفاهی | ثبات دست و بازو | انعطاف‌پذیری بستار | استدلال قیاسی | بیان شفاهی | وضوح گفتار | توجه شنیداری | حساسیت شنوایی | توجه انتخابی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی هوافضا و عملیات هوانوردی | تکنسین‌ها و مکانیک‌های هواپیما | تکنسین‌های مهندسی خودرو | تکنسین‌ها و مکانیک‌های خدمات خودرویی | بازرسان هوانوردی و فرودگاهی | مکانیک‌های اتوبوس، کامیون و متخصصان موتورهای دیزلی | کاردان‌ها و تکنسین‌های کالیبراسیون | بازرسان سازه و ساختمان | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی ناوگان ترابری | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | مهندسان ایمنی و بهداشت حرفه‌ای (به‌جز مهندسان و بازرسان ایمنی معدن) | بازرسان، آزمون‌گران، تفکیک‌کنندگان، نمونه‌برداران و متصدیان توزین | لکوموتیورانان | کارگران تعمیرات و نگهداری عمومی تاسیسات | کارشناسان ایمنی و بهداشت حرفه‌ای | تعمیرکاران واگن‌های راه‌آهن | رئیسان قطار و سرپرستان ایستگاه راه‌آهن | مهندسان کشتی | مهندسان تاسیسات و اپراتورهای بویلرها و دیگ‌های بخار | بازرسان ترابری و حمل‌ونقل</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مکانیک و تکنسین خدمات هواپیما | تکنسین‌های مهندسی خودرو | مکانیک و تکنسین خدمات خودرو | بازرسان هوانوردی و فرودگاهی | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | تکنسین‌ها و کارشناسان فنی کالیبراسیون | بازرسان ساخت‌وساز و ساختمان | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | لکوموتیورانان | کارگران عمومی تعمیرات و نگهداری تاسیسات | کارشناسان بهداشت حرفه‌ای و ایمنی کار | تعمیرکار واگن قطار | رؤسای قطار و مدیران محوطه راه‌آهن | مهندسان فنی کشتی | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | بازرسان ترابری و حمل‌ونقل</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,17 +959,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>نرم‌افزار زمان‌بندی و نوبت‌دهی | نرم‌افزار ثبت ساعت کاری | نرم‌افزار Microsoft Word | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Windows | نرم‌افزار ایمیل</t>
+          <t>نرم‌افزار زمان‌بندی قرار ملاقات | نرم‌افزار ایمیل | نرم‌افزار Microsoft Office | Microsoft Windows | نرم‌افزار Microsoft Windows | نرم‌افزار ایمیل</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نظارت | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ترابری و حمل‌ونقل | زبان انگلیسی | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی</t>
+          <t>حمل و نقل | زبان انگلیسی | ایمنی و امنیت عمومی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>سرپرستان جابه‌جایی بار و بارگیری هواپیما | کارشناسان عملیات فرودگاهی | باربران هتل و چمدان‌بران | رانندگان اتوبوس‌های شهری و بین‌شهری | راهنمایان پذیرش و خدمات هتل (کانسیرژ) | اعزام‌کنندگان و دیسپچرهای ترابری (به‌جز پلیس، آتش‌نشانی و اورژانس) | سرپرستان رده‌اول مهمانداران و متصدیان خدمات مسافران | مهمانداران هواپیما | میزبانان و پذیرش‌کنندگان رستوران و سالن‌های پذیرایی | متصدیان پذیرش هتل و متل | متصدیان رختکن و اتاق‌های تعویض لباس | بهیاران و کمک‌بهیاران | متصدیان پارکینگ | رئیسان قطار و سرپرستان ایستگاه راه‌آهن | متصدیان فروش و رزرو بلیت و خدمات سفر | ناظران سرویس‌های مدارس | رانندگان سرویس و تشریفات | اپراتورهای مترو و قطار شهری | رانندگان تاکسی | راهنمایان سالن، متصدیان لابی و کنترل‌کنندگان بلیت</t>
+          <t>سرپرستان بارگیری و جابه‌جایی بار هواپیما | کارشناسان عملیات فرودگاهی | متصدیان حمل بار و خدمات هتل | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | متصدیان تشریفات و خدمات میهمانان | متصدیان دیسپاچ و اعزام | سرپرستان رده‌اول مهمانداران و خدمه مسافری | مهمانداران هواپیما | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | متصدیان رختکن، امانات و اتاق پرو | خدمات‌دهندگان و انتقال‌دهندگان بیمار | متصدیان پارکینگ | رؤسای قطار و مدیران محوطه راه‌آهن | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | مراقبین و متصدیان سرویس مدارس | رانندگان خودروهای سرویس و تشریفات | رانندگان مترو و تراموا | رانندگان تاکسی | راهنماها، متصدیان سالن و بلیط‌گیرها</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ترابری و حمل‌ونقل | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | مکانیک | جغرافیا</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | زبان انگلیسی | مکانیک | جغرافیا</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی اندام‌ها | دقت کنترل | قدرت ایستا | استحکام بالاتنه | استقامت بدنی | دید نزدیک | دید دور | ادراک عمق | هماهنگی عمومی بدن | تعادل عمومی بدن | انعطاف‌پذیری دامنه حرکتی | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متصدیان خدمات و سوخت‌رسانی فرودگاهی | متصدیان پارکینگ | متصدیان جایگاه‌های سوخت و خدمات وسایل نقلیه و شناورها | مهمانداران و متصدیان خدمات مسافران | متصدیان پل‌های متحرک و حوضچه‌های آرامش | تکنسین‌های ترافیک | بازرسان ترابری و حمل‌ونقل | بازرسان هوانوردی و فرودگاهی | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی) | کارشناسان عملیات فرودگاهی | مهمانداران هواپیما | اپراتورهای تراکتور و لیفتراک‌های صنعتی | کارگران ساده و جابه‌جایی بار، کالا و بسته‌ها | کارگران شست‌وشوی وسایل نقلیه و تجهیزات | متصدیان بار و لجستیک کالا | اعزام‌کنندگان و دیسپچرهای ترابری (به‌جز پلیس، آتش‌نشانی و اورژانس) | رانندگان کامیونت و وانت‌بار | سرپرستان رده‌اول سایر کارکنان حوزه ترابری و حمل‌ونقل | سرپرستان رده‌اول مهمانداران و متصدیان خدمات مسافران | مدیران ترابری، انبارداری و توزیع</t>
+          <t>متصدیان خدمات زمینی و سوخت‌رسانی فرودگاهی | متصدیان پارکینگ | متصدیان جایگاه‌های سوخت و خدمات وسایل نقلیه و شناورها | مهمانداران و متصدیان خدمات مسافران | متصدیان پل‌های متحرک و حوضچه‌های آرامش | تکنسین‌های ترافیک | بازرسان ترابری و حمل‌ونقل | بازرسان هوانوردی و فرودگاهی | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی) | کارشناسان عملیات فرودگاهی | مهمانداران هواپیما | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | کارگزاران حمل‌ونقل و بار | متصدیان دیسپاچ و اعزام | رانندگان خودروهای باربری سبک و وانت‌بارها | سرپرستان رده‌اول سایر کارکنان ترابری و حمل‌ونقل | سرپرستان رده‌اول مهمانداران و خدمه مسافری | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
